--- a/tabular/reference/erv_derived_elements/ervr_data.xlsx
+++ b/tabular/reference/erv_derived_elements/ervr_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/sublineage/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/erv_derived_elements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B57713E-5B20-B543-8AA7-E4F6153DEE77}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AA01E9-CC84-A84D-A43F-565066184C35}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2220" yWindow="860" windowWidth="23060" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="237">
   <si>
     <t>sequenceID</t>
   </si>
@@ -739,6 +739,9 @@
   </si>
   <si>
     <t>degraded_erv_group</t>
+  </si>
+  <si>
+    <t>NK</t>
   </si>
 </sst>
 </file>
@@ -904,7 +907,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1120,6 +1123,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8AD8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1281,7 +1290,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -1312,6 +1321,7 @@
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1380,6 +1390,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF8AD8"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2412,7 +2427,7 @@
         <v>14</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>37</v>
+        <v>236</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="2" t="s">
@@ -2463,7 +2478,7 @@
         <v>14</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>37</v>
+        <v>236</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="2" t="s">
@@ -2514,7 +2529,7 @@
         <v>14</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>37</v>
+        <v>236</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="2" t="s">
@@ -2564,7 +2579,7 @@
       <c r="I17" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="18" t="s">
         <v>37</v>
       </c>
       <c r="K17" s="1"/>
